--- a/open-features.xlsx
+++ b/open-features.xlsx
@@ -9,18 +9,20 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open features" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All features" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions pending" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Go-live blockers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Switched off in prod" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open features" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All features" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions pending" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Go-live blockers" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$4:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Products'!$A$1:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Open features'!$A$1:$I$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All features'!$A$1:$J$268</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions pending'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Go-live blockers'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$4:$C$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Products'!$A$1:$L$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Switched off in prod'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open features'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'All features'!$A$1:$J$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Decisions pending'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Go-live blockers'!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +48,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +82,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE5CD"/>
       </patternFill>
     </fill>
@@ -96,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,6 +131,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -491,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -502,14 +512,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GoKesari - features and products status (18 Oct 2026)</t>
+          <t>GoKesari - features and products status (19 Oct 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: docs/gokesari-audit/GOKESARI_FEATURE_STATUS_REPORT_2026-10-18.xlsx (267 features). Production = main @c96cd04 (gokesari.com, migrations to 0078, last release #185 on 16 Oct). Test site = staging, same code. Status = development status from code, PRs, docs and recorded test runs - not QA sign-off. Replaces the 3 Oct version of this file.</t>
+          <t>Source: docs/gokesari-audit/GOKESARI_FEATURE_STATUS_REPORT_2026-10-19.xlsx (267 features). Production = main @418392d (gokesari.com, migrations to 0084; build &amp; integrate batch live since release #194 on 18 Oct, new features OFF until switched on). Test site = staging, same code. Status = development status from code, PRs, docs and recorded test runs - not QA sign-off. Replaces the 3 Oct version of this file.</t>
         </is>
       </c>
     </row>
@@ -552,11 +562,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>85% - built, merged and live on gokesari.com (incl. built but switched off by default)</t>
+          <t>93% - built, merged and live on gokesari.com (incl. built but switched off by default)</t>
         </is>
       </c>
     </row>
@@ -567,11 +577,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Mobile apps (store builds) and the database split</t>
+          <t>Mobile apps - Android builds done, store publishing on hold</t>
         </is>
       </c>
     </row>
@@ -582,7 +592,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -597,95 +607,125 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Known gaps and planned items with no code yet</t>
+          <t>Known gaps with no code yet (incl. signature capture, deferred to Phase 2)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Products / modules tracked</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>See the "Products" sheet (incl. Inventory &amp; Accounting and Bulk product upload)</t>
+          <t>Online reference prices (GS-023) - dropped by owner decision</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Decisions / vendor choices pending</t>
+          <t>Completed but switched off in production</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>See "Decisions pending"</t>
+          <t>Built and released; waiting for owner keys / a switch (see Go-live blockers)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Go-live blockers open</t>
+          <t>Products / modules tracked</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>See "Go-live blockers"</t>
+          <t>See the "Products" sheet (incl. Inventory &amp; Accounting and Bulk product upload)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Change since 3 Oct</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>+95 completed</t>
-        </is>
+          <t>Decisions / vendor choices pending</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>3 Oct: 132 of 157 complete (84 %); 18 Oct: 227 of 267 (85 %) - 110 features added to the register since 3 Oct</t>
+          <t>See "Decisions pending"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Change since 16 Oct</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>No status change</t>
-        </is>
+          <t>Go-live blockers and owner inputs open</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>20</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>#184 (PMD loader fix) released by #185; #186 / #187 staging sync; #188 docs (open)</t>
+          <t>See "Go-live blockers" (keys, accounts, security actions, inputs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Change since 18 Oct</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>+20 completed</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>18 Oct: 227 of 267 (85 %); 19 Oct: 247 of 267 (92.5 %) - batch #190 released by #194; 23 features changed status</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Change since 3 Oct</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>+115 completed</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>3 Oct: 132 of 157 complete (84 %) - 110 features added to the register since 3 Oct</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C14"/>
+  <autoFilter ref="A4:C16"/>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
@@ -699,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -707,11 +747,13 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -742,25 +784,35 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>of which switched off in prod</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Yet to start</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Dropped</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>% complete</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Open feature IDs</t>
         </is>
@@ -786,23 +838,29 @@
         <v>57</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>GS-023, WF-001, SM-006, NAV-003, GAP-008, GAP-011, GAP-012, GAP-013, GAP-014, GAP-015, GAP-018, GAP-019</t>
+      <c r="I2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>GS-023, GAP-008, GAP-011, GAP-012, GAP-013, GAP-014, GAP-015, GAP-018, GAP-019</t>
         </is>
       </c>
     </row>
@@ -829,7 +887,7 @@
         <v>39</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>0</v>
@@ -837,10 +895,16 @@
       <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -868,19 +932,27 @@
       <c r="E4" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>0.88</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>IA-022, IA-031, IA-032, IA-034, IA-039, IA-049, IA-056</t>
         </is>
@@ -908,19 +980,27 @@
       <c r="E5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>0.88</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>BPU-10, BPU-11</t>
         </is>
@@ -937,32 +1017,38 @@
           <t>Master product catalogue, feeds, loader, quality scores</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>LIVE - work open</t>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>PMD-002, PMD-006, PMD-007</t>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -986,23 +1072,29 @@
         <v>30</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="H7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>GAP-001, GAP-002, GAP-003, GAP-004</t>
+      <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>GAP-003</t>
         </is>
       </c>
     </row>
@@ -1026,23 +1118,29 @@
         <v>19</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>GS-028, SM-005, NEW-007, NEW-027, GAP-005, GAP-006</t>
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>NEW-027</t>
         </is>
       </c>
     </row>
@@ -1077,10 +1175,16 @@
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1117,10 +1221,16 @@
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1157,10 +1267,16 @@
       <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1177,32 +1293,38 @@
           <t>Sign-in (Google, email, mobile), roles, RBAC, data protection</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>LIVE - work open</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
         <v>26</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>GS-001, RBAC-003</t>
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1226,23 +1348,29 @@
         <v>13</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F13" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>GS-073, GS-074, NEW-037, GAP-009</t>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>GAP-009</t>
         </is>
       </c>
     </row>
@@ -1269,18 +1397,24 @@
         <v>2</v>
       </c>
       <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>NEW-043, PLT-017</t>
         </is>
@@ -1306,28 +1440,34 @@
         <v>31</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>PLT-009, PLT-015, QA-003, QA-009, GAP-010, GAP-016, GAP-017</t>
+        <v>2</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>PLT-015, QA-003, QA-009, GAP-010, GAP-016, GAP-017</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J15"/>
+  <autoFilter ref="A1:L15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1338,7 +1478,1258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Product / module</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Switch / what it needs</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Remaining / owner input</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Blocked on / next step</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>GS-014</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Product images/specifications</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Seller Central (shop owner portal)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - switch on in Admin &gt; Business rules (rule: imageModeration.enabled)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>GS-027</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Delivery slot</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Customer shopping (web + app)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - switch on in Admin &gt; Business rules (rules: scheduledSlots.enabled, deliverySlots.enabled)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>GS-028</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>UPI/card/netbanking gateway</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Off until live gateway keys (onlinePayments); sandbox on test</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Live Cashfree / Razorpay / PhonePe keys and webhook secrets</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>GS-033</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Shop order split</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Customer shopping (web + app)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - switch on in Admin &gt; Business rules (rule: parentOrders.enabled)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>GS-054</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Referral program</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Notifications, integrations &amp; marketing</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - switch on in Admin &gt; Business rules (rule: customerReferrals.enabled; rewards Rs 50 / Rs 50)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>GS-072</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Maps/navigation</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Notifications, integrations &amp; marketing</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - switch on in Admin &gt; Business rules (rule: routing.enabled)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>In-app turn-by-turn navigation not built (Google Maps deep link used instead).</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>GS-073</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Payment gateway</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Notifications, integrations &amp; marketing</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Off until live gateway keys</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Live keys and webhook secrets</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>GS-074</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SMS/WhatsApp/email/push</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Notifications, integrations &amp; marketing</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Email + in-app live; Expo push on mock until EAS / FCM / APNs keys; SMS / WhatsApp stubs</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Real push keys; SMS / WhatsApp vendor if wanted</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §11 (push)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>WF-001</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Customer product purchase</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Customer shopping (web + app)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Online payment at checkout built (sandbox); live keys needed</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Live gateway keys</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>RBAC-003</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Manage own shop</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Identity, access &amp; security</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>OPERATOR_LIMITED role live on test; production by role grant</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SM-005</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Payment state machine</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Off until live gateway keys</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>RECONCILED / CHARGEBACK states not added</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>GA-005</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Current load</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Delivery &amp; riders (gig)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - switch on in Admin &gt; Business rules (rule: batching.enabled; F3 busy-rider fallback: dispatch.busyRidersAsFallback)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>NAV-001</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Customer portal - Home</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Customer shopping (web + app)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - switch on in Admin &gt; Business rules (rule: homePriceComparison.enabled)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>The category grid was deliberately removed in favour of search-first; categories are reachable from shops and search.</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>NAV-002</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Customer portal - Shop</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Customer shopping (web + app)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - switch on in Admin &gt; Business rules (rule: shopOffers.enabled)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>NAV-003</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Customer portal - Cart &amp; Checkout</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Customer shopping (web + app)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Online payment at checkout built (sandbox); coupons rule unchanged</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Live gateway keys</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>NEW-007</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Direct per-order payments, tax invoicing, photo POD, accept timeout</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>All four parts built; per-order online payment off until live keys</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Live gateway keys; CA to confirm invoice rates / HSN (NEW-027)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>NEW-020</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Cancellation before packing - full refund; optional customer cancel until packing (item A)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Customer shopping (web + app)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - rule cancellation.customerMayCancelUntil = CONFIRMED (the original behaviour); PREPARING turns it on</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Choose whether to switch PREPARING on</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>NEW-033</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Shop prepaid wallet</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - rule shopWallet.enabled = false (on for the test site only)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Production release</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Legal review of holding shops' prepaid money (Blockers #17) before switching it on</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>NEW-034</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Shop wallet: Rs 5/km delivery charge, no checkout below minimum, commission back on refunds</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - rule shopWallet.enabled = false (on for the test site only)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Production release</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Legal review of holding shops' prepaid money (Blockers #17) before switching it on</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>NEW-038</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Shop self-registration with auto-approval (Module 3)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Seller Central (shop owner portal)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - rule selfRegistration.enabled = false; refused on gokesari.com until a real SMS/WhatsApp provider is set</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Merge #92; real SMS / WhatsApp provider for production (refused on gokesari.com until set); fee amounts; FSSAI rule for self-registered food shops</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs P2, P4, P5 (Blockers #18) before switching it on</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>NEW-039</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Delivery options and scheduling: pickup, shop's own delivery, GoKesari partner</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Delivery &amp; riders (gig)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - rule fulfilmentOptions.enabled = false (on for the test site only)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Production release (migrations 0056-0064); owner decision F1-8 - refund the customer's delivery fee automatically when the shop chooses pickup?</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Switch on in Admin &gt; Business rules when ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>NEW-040</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory legal documents by shop type (FSSAI, drug licence, medical registration)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Seller Central (shop owner portal)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - rule legalDocuments.enabled = false (on for the test site only)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Production release; tell shop owners about the 15-day grace first; decision - also hide shops past their grace period from customers?</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Tell shop owners about the 15-day grace, then switch on (Blockers #28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>NEW-041</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Bank account details with Rs 1 verification (shops for payouts, customers for refunds)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - rule bankAccounts.enabled = false (on for the test site only)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Production release; Cashfree live keys with the Refunds API; payout gate not run on test (covered by integration tests); decisions - buy Cashfree Verification Suite for the bank's name? offer refunds to bank at all?</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Cashfree live keys with the Refunds API (Blockers #24), then switch on</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>NEW-042</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory referral code at shop registration + 'Request a referral code'</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Seller Central (shop owner portal)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Admin &gt; Referral settings: referral_required_shop = OPTIONAL on production (checked 14 Oct)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Production release; create referral codes before switching it on (or registrations stop); confirm who owns referrals@gokesari.com and that mail arrives there</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Create referral codes and the referrals@ mailbox (Blockers #26), then switch on</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>NEW-048</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory customer referral code at sign-up, with 'ask us for a code'</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Notifications, integrations &amp; marketing</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Admin &gt; Referral settings: referral_required_customer = OPTIONAL on production (checked 14 Oct)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Set requiredFrom and switch on when codes can be issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>NEW-049</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Refunds to the customer's verified bank account</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - rule bankRefunds.enabled = false</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Switch on with bank accounts (NEW-041)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>NEW-050</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Bank account checked with the bank (Cashfree Verification Suite) instead of the Rs 1 payment</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Off by default - rule bankAccountCheck.enabled = false</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Test site showed 'Keys not found' before #117</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Verification Suite keys on production, then switch on</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>PMD-002</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>GS1 India and manufacturer-catalogue feeds</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Product Master Data Platform</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturer portal on; GS1 DataKart (mock) and Open Food Facts off (Admin &gt; Settings)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>GS1 India Solution Provider agreement and keys for live GS1 data</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>PLT-013</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Opt-in prepared statements (DATABASE_PREPARED_STATEMENTS=on)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Platform, performance &amp; QA</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Off - environment variable not set on either site</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Turn on for test.gokesari.com, check Neon's pooled host accepts prepared statements, then gokesari.com</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Owner: environment setting (Blockers #36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>GAP-001</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Pickup QR code</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Delivery &amp; riders (gig)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Off - rule pickupQr.enabled; set PICKUP_QR_SECRET first</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Owner: switch on</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>GAP-002</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>In-app turn-by-turn navigation</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Delivery &amp; riders (gig)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Off - rule riderNavigation.enabled; Google Routes / OSRM provider (mock on test)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Routes API on the Maps server key, or an OSRM server</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Owner: provider + switch on</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>GAP-004</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Broadcast job offers / radius widening</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Delivery &amp; riders (gig)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Off - rule dispatchBroadcast.enabled (radius 2 &gt; 4 &gt; 6 km)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Owner: switch on (needs the timeout-sweep cron)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>GAP-005</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Automated bank transfer for settlements and rider payouts</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Off - PayoutProvider on sandbox</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>RazorpayX / Cashfree payout keys</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>GAP-006</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Platform tax invoice for GoKesari's own fees (D6)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Payments, wallet &amp; finance</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Off until GoKesari GSTIN, legal details and invoice prefix</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>CA to confirm TCS / TDS / SAC rates</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs §4-6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G35"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1450,22 +2841,22 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>GS-023</t>
+          <t>PLT-017</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>E-commerce price benchmark</t>
+          <t>'iPhone app' workflow - EAS build and TestFlight upload</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Customer shopping (web + app)</t>
+          <t>Mobile apps (Android / iPhone)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -1475,17 +2866,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>GitHub Actions (runs from main)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Turn on the customer display - one rule flip, no code.</t>
+          <t>Link the project to Expo and commit the project id; secrets EXPO_TOKEN, ASC_API_KEY_P8, ASC_KEY_ID, ASC_ISSUER_ID, APPLE_TEAM_ID; App Store Connect app record for com.gokesari.app</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>D7 - lawful / licensed price source</t>
+          <t>On hold (owner decision on store publishing); then EXPO_TOKEN + Expo project id</t>
         </is>
       </c>
     </row>
@@ -1495,17 +2886,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>NAV-003</t>
+          <t>NEW-027</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Customer portal - Cart &amp; Checkout</t>
+          <t>GST rates / HSN codes report for the CA; cron map (item D)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Customer shopping (web + app)</t>
+          <t>Payments, wallet &amp; finance</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1520,17 +2911,17 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production (gokesari.com)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Online payment at checkout.</t>
+          <t>CA to verify HSN codes, GST rates, bill-of-supply wording and invoice numbering before invoicing is used for filing</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Needs GS-028</t>
+          <t>CA verification</t>
         </is>
       </c>
     </row>
@@ -1540,17 +2931,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SM-006</t>
+          <t>GAP-010</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Issue state machine</t>
+          <t>Slow signed-in pages and cold first visits (database far from the web server)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Customer shopping (web + app)</t>
+          <t>Platform, performance &amp; QA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1565,17 +2956,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Either add the four states to grievances or accept the dispute lifecycle as the issue state machine.</t>
+          <t>Database and web server in the same region and a longer idle timeout; then prepared statements (PLT-013)</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Decision: does the dispute lifecycle satisfy SM-006?</t>
+          <t>Owner: hosting decision (Blockers #35)</t>
         </is>
       </c>
     </row>
@@ -1585,17 +2976,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>WF-001</t>
+          <t>PLT-015</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Customer product purchase</t>
+          <t>Seller / customer database split (tooling and 'Database split' workflow)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Customer shopping (web + app)</t>
+          <t>Platform, performance &amp; QA</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1610,17 +3001,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>GitHub Actions (runs from main)</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Direct online payment for the order.</t>
+          <t>Cut-over (DB_SPLIT_MODE) not performed</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Needs GS-028</t>
+          <t>Owner: go-ahead and window for the cut-over + Neon logical replication (Owner inputs §13)</t>
         </is>
       </c>
     </row>
@@ -1630,22 +3021,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>GS-001</t>
+          <t>QA-003</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Mobile/email/Gmail login</t>
+          <t>Execute the 791 test cases and sign off in a browser on test.gokesari.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Identity, access &amp; security</t>
+          <t>Platform, performance &amp; QA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1655,17 +3046,17 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>SMS delivery of the OTP so a mobile number is proven (OTP provider seam ready).</t>
+          <t>Manual 791-case browser plan still not run; production order-lifecycle subset not run</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>D2 - SMS/OTP vendor with DLT registration</t>
+          <t>Owner inputs §14 (production shop, rider, payment choice)</t>
         </is>
       </c>
     </row>
@@ -1675,17 +3066,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>RBAC-003</t>
+          <t>QA-009</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Manage own shop</t>
+          <t>Order-lifecycle run on production (gokesari.com) with a real payment</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Identity, access &amp; security</t>
+          <t>Platform, performance &amp; QA</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1700,17 +3091,17 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Define what an operator may change on a shop, then implement.</t>
+          <t>Needs the owner's production shop and owner email, an approved rider, Cashfree live keys confirmed, and the owner to pay the top-up</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Decision: what 'Limited' means</t>
+          <t>Owner inputs §14</t>
         </is>
       </c>
     </row>
@@ -1720,12 +3111,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PLT-017</t>
+          <t>NEW-043</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>'iPhone app' workflow - EAS build and TestFlight upload</t>
+          <t>Android and iPhone app (mobile/) - native shell around gokesari.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1738,24 +3129,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>GitHub Actions (runs from main)</t>
+          <t>Mobile app - Android test builds only (not in stores)</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Link the project to Expo and commit the project id; secrets EXPO_TOKEN, ASC_API_KEY_P8, ASC_KEY_ID, ASC_ISSUER_ID, APPLE_TEAM_ID; App Store Connect app record for com.gokesari.app</t>
+          <t>Store publishing on hold (owner decision)</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Owner: Apple Developer account and the secrets (Blockers #29)</t>
+          <t>Owner: decide when to publish (Play / App Store)</t>
         </is>
       </c>
     </row>
@@ -1765,42 +3156,42 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>GS-073</t>
+          <t>GAP-011</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Payment gateway</t>
+          <t>Search shows '0 shops' for products that nearby shops sell</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Notifications, integrations &amp; marketing</t>
+          <t>Customer shopping (web + app)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Order payment intents, callbacks and gateway refunds.</t>
+          <t>Fix shop matching in search (back-end)</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Needs GS-028</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1810,42 +3201,42 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>GS-074</t>
+          <t>GAP-012</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>SMS/WhatsApp/email/push</t>
+          <t>Admin dispute resolution gives no visible confirmation</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Notifications, integrations &amp; marketing</t>
+          <t>Customer shopping (web + app)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Real SMS / push / WhatsApp providers.</t>
+          <t>Busy state and success message on the resolve form</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>D2 - vendor choice (DLT registration)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1855,17 +3246,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>NEW-037</t>
+          <t>GAP-013</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Accounting / inventory integration and GST (Module 2)</t>
+          <t>Approved return waiting for a rider cannot be completed by staff</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Notifications, integrations &amp; marketing</t>
+          <t>Customer shopping (web + app)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1873,24 +3264,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Merge #92; real GSP and sandbox keys; Tally code-signing certificate; CA answers on e-commerce operator questions (TCS / GSTR-8)</t>
+          <t>Decide whether staff may complete a pickup without a rider</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Owner inputs P1, P3, P6 (Blockers #18)</t>
+          <t>Owner: business rule</t>
         </is>
       </c>
     </row>
@@ -1900,42 +3291,42 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>GS-028</t>
+          <t>GAP-014</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>UPI/card/netbanking gateway</t>
+          <t>/orders?tab=returns shows the Active list</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Payments, wallet &amp; finance</t>
+          <t>Customer shopping (web + app)</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Per-order ONLINE payment via Cashfree hosted checkout (design signed off 1 Oct).</t>
+          <t>Map tab=returns to /returns</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Go-ahead to build per-order payment, or a decision to launch wallet + COD only</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1945,17 +3336,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>NEW-007</t>
+          <t>GAP-015</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Direct per-order payments, tax invoicing, photo POD, accept timeout</t>
+          <t>Hindi / Marathi for the body of inner pages</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Payments, wallet &amp; finance</t>
+          <t>Customer shopping (web + app)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1963,24 +3354,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Per-order online payment only (the other three parts are done). Invoice rates / HSN / wording to be confirmed by a CA before use for filing.</t>
+          <t>Translate the remaining strings with a native-speaker review</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Per-order online payment go-ahead (GS-028)</t>
+          <t>Owner: decision (Blockers #38)</t>
         </is>
       </c>
     </row>
@@ -1990,17 +3381,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>NEW-027</t>
+          <t>GAP-018</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>GST rates / HSN codes report for the CA; cron map (item D)</t>
+          <t>My Orders card wording after an order is switched to pickup</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Payments, wallet &amp; finance</t>
+          <t>Customer shopping (web + app)</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -2008,24 +3399,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Production (gokesari.com)</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>CA to verify HSN codes, GST rates, bill-of-supply wording and invoice numbering before invoicing is used for filing</t>
+          <t>Hide the rider line once the order is not a GoKesari delivery; label the delivery-fee refund correctly</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>CA verification</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2035,17 +3426,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SM-005</t>
+          <t>GAP-019</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Payment state machine</t>
+          <t>Wallet checkout takes 30-38 s on the test site</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Payments, wallet &amp; finance</t>
+          <t>Customer shopping (web + app)</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -2053,24 +3444,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>INITIATED -&gt; AUTHORIZED -&gt; CAPTURED -&gt; RECONCILED; CHARGEBACK.</t>
+          <t>Profile checkout on test; likely the far database (GAP-010)</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Per-order online payment go-ahead (GS-028 / NEW-007)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2080,17 +3471,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>GAP-010</t>
+          <t>GAP-003</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Slow signed-in pages and cold first visits (database far from the web server)</t>
+          <t>Signature capture at delivery</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Platform, performance &amp; QA</t>
+          <t>Delivery &amp; riders (gig)</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2098,9 +3489,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -2110,12 +3501,12 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Database and web server in the same region and a longer idle timeout; then prepared statements (PLT-013)</t>
+          <t>Deferred to Phase 2 (owner decision)</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Owner: hosting decision (Blockers #35)</t>
+          <t>Phase 2</t>
         </is>
       </c>
     </row>
@@ -2125,17 +3516,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>PLT-009</t>
+          <t>GAP-009</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>'Production database' workflow (verify / migrate with typed confirmation)</t>
+          <t>Email sending capacity (mail host hourly limit)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Platform, performance &amp; QA</t>
+          <t>Notifications, integrations &amp; marketing</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2143,24 +3534,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>GitHub Actions (runs from main)</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Repository-level secrets/variables are not set</t>
+          <t>Raise the limit with the host or send through a transactional email service; check SPF/DKIM</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Owner: PROD_DATABASE_URL is still not visible to Actions - nine copy-shops / db-split plan or verify runs got an empty value (Blockers #32)</t>
+          <t>Owner: email provider choice</t>
         </is>
       </c>
     </row>
@@ -2170,12 +3561,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>QA-009</t>
+          <t>GAP-016</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Order-lifecycle run on production (gokesari.com) with a real payment</t>
+          <t>Same Drizzle bare-id subquery bug in rider reliability and the integrations 'listed' flag</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2188,9 +3579,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -2200,12 +3591,12 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Needs the owner's production shop and owner email, an approved rider, Cashfree live keys confirmed, and the owner to pay the top-up</t>
+          <t>Apply the #138 fix pattern and add regression tests</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Owner: the four inputs (Blockers #44)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2215,17 +3606,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>PMD-002</t>
+          <t>GAP-017</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>GS1 India and manufacturer-catalogue feeds</t>
+          <t>React error #418 (hydration) on /wallet and /admin/orders</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Product Master Data Platform</t>
+          <t>Platform, performance &amp; QA</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2233,24 +3624,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Production (gokesari.com)</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Load real GS1 / brand data</t>
+          <t>Find the server / client difference and fix</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>GS1 India agreement and brand permissions, plus a real sample file for each</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2260,952 +3651,52 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>NEW-043</t>
+          <t>GS-023</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Android and iPhone app (mobile/) - native shell around gokesari.com</t>
+          <t>E-commerce price benchmark</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Mobile apps (Android / iPhone)</t>
+          <t>Customer shopping (web + app)</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>DROPPED</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Mobile app - Android test builds only (not in stores)</t>
+          <t>Dropped (code constant)</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Expo account + EAS project id; Google Play Console ($25) and first .aab upload; Apple Developer Program ($99/yr) for any iPhone install; store listings (privacy policy, Data safety form, screenshots)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Owner: Apple Developer account, then the iPhone build secrets (PLT-017); Google Play account for Android</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>PLT-015</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Seller / customer database split (tooling and 'Database split' workflow)</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Platform, performance &amp; QA</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>GitHub Actions (runs from main)</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Production split: run 19 (migrate, 14 Oct 14:08-14:12 UTC) PASSED: 190 tables, 486 rows, every checksum equal, 0 missing parents on 111 links (report artifact db-split-report-production). But the two production split secrets point at databases literally named PROD_SELLER_DATABASE_URL and PROD_CUSTOMER_DATABASE_URL (test uses gokesari_seller / gokesari_customer) - check the secret values. Then phases 2-4 (shadow writes / replication, switching reads and writes, contract) are not started.</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Owner: check the production split secrets (Blockers #42); then plan phases 2-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>GAP-011</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Search shows '0 shops' for products that nearby shops sell</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Customer shopping (web + app)</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Fix shop matching in search (back-end)</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>GAP-012</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Admin dispute resolution gives no visible confirmation</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Customer shopping (web + app)</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Busy state and success message on the resolve form</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>GAP-013</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Approved return waiting for a rider cannot be completed by staff</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Customer shopping (web + app)</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Decide whether staff may complete a pickup without a rider</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Owner: business rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>GAP-014</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>/orders?tab=returns shows the Active list</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Customer shopping (web + app)</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Map tab=returns to /returns</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>GAP-015</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Hindi / Marathi for the body of inner pages</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Customer shopping (web + app)</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Translate the remaining strings with a native-speaker review</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Owner: decision (Blockers #38)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>GAP-018</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>My Orders card wording after an order is switched to pickup</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Customer shopping (web + app)</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Hide the rider line once the order is not a GoKesari delivery; label the delivery-fee refund correctly</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>GAP-019</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Wallet checkout takes 30-38 s on the test site</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Customer shopping (web + app)</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Profile checkout on test; likely the far database (GAP-010)</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>GAP-001</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Pickup QR code</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Delivery &amp; riders (gig)</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Build if wanted</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>GAP-002</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>In-app turn-by-turn navigation</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Delivery &amp; riders (gig)</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Build if wanted</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>GAP-003</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Signature capture at delivery</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Delivery &amp; riders (gig)</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Build if wanted</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>GAP-004</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Broadcast job offers / radius widening</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Delivery &amp; riders (gig)</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Build if wanted</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>GAP-009</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Email sending capacity (mail host hourly limit)</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Notifications, integrations &amp; marketing</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Raise the limit with the host or send through a transactional email service; check SPF/DKIM</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Owner: email provider choice</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>GAP-005</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Automated bank transfer for settlements and rider payouts</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Payments, wallet &amp; finance</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Payout-API integration</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>GAP-006</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Platform tax invoice for GoKesari's own fees (D6)</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Payments, wallet &amp; finance</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Platform invoice + SAC</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>D6 settlement model (pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>GAP-016</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Same Drizzle bare-id subquery bug in rider reliability and the integrations 'listed' flag</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Platform, performance &amp; QA</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Apply the #138 fix pattern and add regression tests</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>GAP-017</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>React error #418 (hydration) on /wallet and /admin/orders</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Platform, performance &amp; QA</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>Find the server / client difference and fix</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>QA-003</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Execute the 791 test cases and sign off in a browser on test.gokesari.com</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Platform, performance &amp; QA</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>Run phases 1-4 and record results</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>PMD-006</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Large-scale ingestion (pilot step 9)</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Product Master Data Platform</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Whole step</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Explicit go-ahead; licensed feeds (PMD-002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>PMD-007</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Product browser / edit screens, promote button, scheduler and alerting</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Product Master Data Platform</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Whole item</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I41"/>
+  <autoFilter ref="A1:I21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3307,24 +3798,24 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production (gokesari.com)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Live (email OTP); SMS OTP not available</t>
+          <t>Live (email OTP); SMS OTP only via the Phase-2 SMS stub</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>#14; #23; #43; #81; #123</t>
+          <t>#14; #23; #43; #81; #123; #194</t>
         </is>
       </c>
     </row>
@@ -4407,24 +4898,24 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>DROPPED</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Dropped (code constant)</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Hidden from customers (externalPrices.showToCustomers = false)</t>
+          <t>Off permanently (code constant, not a setting)</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>#23</t>
+          <t>#23; #194</t>
         </is>
       </c>
     </row>
@@ -4657,24 +5148,24 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Off until live gateway keys (onlinePayments); sandbox on test</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Baseline; #194</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6665,7 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>#40</t>
+          <t>#40; #194</t>
         </is>
       </c>
     </row>
@@ -6907,24 +7398,24 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Off until live gateway keys</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Baseline; #194</t>
         </is>
       </c>
     </row>
@@ -6957,24 +7448,24 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>Email + in-app live (email needs SMTP)</t>
+          <t>Email + in-app live; Expo push on mock until EAS / FCM / APNs keys; SMS / WhatsApp stubs</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>#23</t>
+          <t>#23; #194</t>
         </is>
       </c>
     </row>
@@ -7007,24 +7498,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Online payment at checkout built (sandbox); live keys needed</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>Baseline; #14; #19; #23; #24; #43; #57</t>
+          <t>Baseline; #14; #19; #23; #24; #43; #57; #194</t>
         </is>
       </c>
     </row>
@@ -7607,24 +8098,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>OPERATOR_LIMITED role live on test; production by role grant</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Baseline; #194</t>
         </is>
       </c>
     </row>
@@ -8457,24 +8948,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Off until live gateway keys</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Baseline; #194</t>
         </is>
       </c>
     </row>
@@ -8507,24 +8998,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production (gokesari.com)</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Live (help desk + grievance portal)</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>#19; #40</t>
+          <t>#19; #40; #194</t>
         </is>
       </c>
     </row>
@@ -9107,24 +9598,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>Coupons: Off by default - switch on in Admin &gt; Business rules (rule: coupons.enabled)</t>
+          <t>Online payment at checkout built (sandbox); coupons rule unchanged</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>Baseline; #23; #43; #71; #57</t>
+          <t>Baseline; #23; #43; #71; #57; #194</t>
         </is>
       </c>
     </row>
@@ -10974,7 +11465,7 @@
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>#14; #23</t>
+          <t>#14; #23; #194</t>
         </is>
       </c>
     </row>
@@ -11007,24 +11498,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G156" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>Off by default - switch on in Admin &gt; Business rules (rules: invoicing.enabled, deliveryProof.photoRequired, shopAcceptance.enabled)</t>
+          <t>All four parts built; per-order online payment off until live keys</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>#23; #65</t>
+          <t>#23; #65; #194</t>
         </is>
       </c>
     </row>
@@ -11674,7 +12165,7 @@
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>#86 (reverted by #87); #120</t>
+          <t>#86 (reverted by #87); #120; #194</t>
         </is>
       </c>
     </row>
@@ -12507,24 +12998,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G186" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>Production - partly live</t>
+          <t>Production (gokesari.com)</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>Shops can connect accounting / inventory software; GST e-invoicing on the MOCK GSP until a real GSP is chosen</t>
+          <t>GST invoice per order live; inventory sync descoped (rule inventorySync OFF)</t>
         </is>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t>#120</t>
+          <t>#120; #194</t>
         </is>
       </c>
     </row>
@@ -14057,24 +14548,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G217" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>Production (gokesari.com)</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t>Sources disabled by design</t>
+          <t>Manufacturer portal on; GS1 DataKart (mock) and Open Food Facts off (Admin &gt; Settings)</t>
         </is>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>#8; #194</t>
         </is>
       </c>
     </row>
@@ -14257,24 +14748,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G221" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Production (gokesari.com)</t>
         </is>
       </c>
       <c r="I221" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Live (admin)</t>
         </is>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#194</t>
         </is>
       </c>
     </row>
@@ -14307,24 +14798,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G222" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Production (gokesari.com)</t>
         </is>
       </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Live (admin product browser)</t>
         </is>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#194</t>
         </is>
       </c>
     </row>
@@ -14757,9 +15248,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G231" s="8" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -14769,12 +15260,12 @@
       </c>
       <c r="I231" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
-          <t>#118</t>
+          <t>#118; #194</t>
         </is>
       </c>
     </row>
@@ -15057,9 +15548,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G237" s="5" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="G237" s="8" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -15357,9 +15848,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G243" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="G243" s="8" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -15374,7 +15865,7 @@
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#194</t>
         </is>
       </c>
     </row>
@@ -15707,24 +16198,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G250" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="G250" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I250" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Off - rule pickupQr.enabled; set PICKUP_QR_SECRET first</t>
         </is>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#194</t>
         </is>
       </c>
     </row>
@@ -15757,24 +16248,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G251" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="G251" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I251" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Off - rule riderNavigation.enabled; Google Routes / OSRM provider (mock on test)</t>
         </is>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#194</t>
         </is>
       </c>
     </row>
@@ -15857,24 +16348,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G253" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="G253" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Off - rule dispatchBroadcast.enabled (radius 2 &gt; 4 &gt; 6 km)</t>
         </is>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#194</t>
         </is>
       </c>
     </row>
@@ -15907,24 +16398,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G254" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="G254" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I254" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Off - PayoutProvider on sandbox</t>
         </is>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#194</t>
         </is>
       </c>
     </row>
@@ -15957,24 +16448,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G255" s="9" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="G255" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Production - built, switched off by default</t>
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Off until GoKesari GSTIN, legal details and invoice prefix</t>
         </is>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#194</t>
         </is>
       </c>
     </row>
@@ -16634,7 +17125,593 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Decision / input</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>What is needed</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Unblocks</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Who</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Which off-by-default features to switch on in production</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Choose which of the now-released off-by-default features to switch on in production: F3-F11 and #58 rules, plus fulfilmentOptions, legalDocuments, bankAccounts, bankRefunds, bankAccountCheck, shopReferral, customerSignupReferral, shopWallet, selfRegistration, cancellation PREPARING (all off on gokesari.com after #120).</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>GS-014, GS-027, GS-033, GS-054, GS-072, GA-005, NAV-001, NAV-002, NAV-003, NEW-007</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Event-layer decisions to confirm</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Dispatch starts at READY; customer not told when a rider declines; shops propose resolutions only after triage; auto-approved shops classified GREEN; 'support' = operators + admins.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>NEW-028, NEW-030, NEW-031</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>PENDING CONFIRMATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Gridlines live keys (seller verification)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Sandbox then live keys; confirm FSSAI / GSTIN fields, Shop Act coverage, IP whitelist, retention and DPA. Production shows verification as paused until then.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>GS-007 automatic checks</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Legal / CA</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CA check of GST rates, HSN codes and invoice wording</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Run scripts/gst-hsn-report.sql and have a CA confirm rates, HSN codes, bill-of-supply wording and numbering before invoicing is used for filing. Update 15 Oct: also covers the GST liability, set-off and invoice figures in Inventory &amp; Accounting (NEW-067, on test).</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>NEW-007 (invoicing), NEW-027</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Owner / CA</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Seller-verification retention and Shop Act needs</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Lawyer/CA to confirm the retention period after closure (default 1,095 days) and Shop Act needs for non-MH / home sellers.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GS-007 compliance</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Owner / lawyer</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Holding shops' prepaid money</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Legal review of the shop prepaid wallet; at least a seller-terms clause.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>NEW-033, NEW-034</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Owner / lawyer</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Agreement</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>GS1 India and brand permissions</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Agreement / written permission and a real sample file for each source; then go-ahead for large-scale ingestion.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>PMD-002, PMD-006</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Cashfree live keys and Refunds API</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Set CASHFREE_APP_ID / CASHFREE_SECRET_KEY / CASHFREE_ENV=production and confirm the Refunds API is enabled - the Rs 1 bank-account check refunds every payment.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>NEW-041</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Tile Board: build the four entries that have no feature behind them?</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Customer Favourites, App theme, Call rider (rider number is not shown to customers today); shop owner Theme. The board shows the nearest real page in their place.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>NEW-046</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Translate the body of inner pages into Hindi / Marathi?</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Boards, header, menus, tabs and error screens are translated; forms, tables and policy pages are English. Thousands of strings; needs a native-speaker review.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>GAP-015; NEW-047</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Decision / vendor</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Accounting: licensed GSP for GST returns</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Choose and contract a GSP (Masters India, ClearTax, IRIS, Tally GSP, Vayana) for live GSTR-2B/2A/1 pull; until then owners upload the file from gst.gov.in (works on production).</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>IA-022, IA-023</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Accounting: AI reading of supplier bills</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Allow bills to be read by Claude (ANTHROPIC_API_KEY + INVOICE_EXTRACTION_PROVIDER=claude): needed for photos, handwriting, Hindi and Marathi. Without it: e-invoice, Excel, PDF text and typing.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>IA-034, IA-039</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Accounting: bill forwarding by email and S3 bucket</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Inbound mail provider (INBOUND_EMAIL_SECRET / _DOMAIN) for forwarding; S3-compatible bucket credentials (ACCOUNTS_S3_*) - bills stay in the database until then.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>IA-032, IA-049</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Legal / CA</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CA confirmation of TCS / TDS / SAC rates</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Rates looked up 18 Oct; CA must confirm before production use</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>GAP-005, GAP-006</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Owner / CA</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Owner choice</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Switch on the new batch features in production</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Every batch feature is OFF on gokesari.com: online payments, broadcast offers, pickup QR (needs PICKUP_QR_SECRET), rider navigation, payouts, fee invoices, push</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>GAP-001, GAP-002, GAP-004, GAP-005, GAP-006, GS-028</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16649,767 +17726,6 @@
     <col width="80" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Decision / input</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>What is needed</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Unblocks</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Who</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Per-order online payment (GS-028 / NEW-007)</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Approve building per-order Cashfree payment, or launch with wallet + COD only.</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>GS-028, GS-073, SM-005, WF-001, NAV-003, NEW-007</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>D2 - SMS / OTP vendor (DLT) and WhatsApp provider</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Pick a DLT-registered SMS provider and a WhatsApp BSP (or Meta Cloud API). Also blocks testing paid self-registration on test (SMS_PROVIDER=none, N-2).</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>GS-001, GS-074, NEW-035 (SMS code), NEW-038</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>D7 - licensed external price source</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Approve a lawful / licensed source for customer-visible reference prices (then one rule flip).</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>GS-023</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>D10 - cancellation after packing</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Confirm READY/ASSIGNED (customer refused) and PICKED_UP/OUT_FOR_DELIVERY (goods-only refund, delivery fee kept).</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>NEW-006 sign-off, NEW-020</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>D6 - delivery fee kept on cancellation; platform invoicing of its own fees</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Decide how the kept delivery fee is shared/reported and how GoKesari invoices its fees (SAC).</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GAP-006</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Owner / CA</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>RBAC-003 - operator 'Limited' shop management</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Define what an operator may change on a shop.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>RBAC-003</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>SM-006 scope</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Accept the dispute lifecycle as the issue state machine, or add its states to grievances.</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>SM-006</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Which off-by-default features to switch on in production</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Choose which of the now-released off-by-default features to switch on in production: F3-F11 and #58 rules, plus fulfilmentOptions, legalDocuments, bankAccounts, bankRefunds, bankAccountCheck, shopReferral, customerSignupReferral, shopWallet, selfRegistration, cancellation PREPARING (all off on gokesari.com after #120).</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>GS-014, GS-027, GS-033, GS-054, GS-072, GA-005, NAV-001, NAV-002, NAV-003, NEW-007</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Event-layer decisions to confirm</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Dispatch starts at READY; customer not told when a rider declines; shops propose resolutions only after triage; auto-approved shops classified GREEN; 'support' = operators + admins.</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>NEW-028, NEW-030, NEW-031</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>PENDING CONFIRMATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Gridlines live keys (seller verification)</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Sandbox then live keys; confirm FSSAI / GSTIN fields, Shop Act coverage, IP whitelist, retention and DPA. Production shows verification as paused until then.</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>GS-007 automatic checks</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Legal / CA</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>CA check of GST rates, HSN codes and invoice wording</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Run scripts/gst-hsn-report.sql and have a CA confirm rates, HSN codes, bill-of-supply wording and numbering before invoicing is used for filing. Update 15 Oct: also covers the GST liability, set-off and invoice figures in Inventory &amp; Accounting (NEW-067, on test).</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>NEW-007 (invoicing), NEW-027</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Owner / CA</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Seller-verification retention and Shop Act needs</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Lawyer/CA to confirm the retention period after closure (default 1,095 days) and Shop Act needs for non-MH / home sellers.</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>GS-007 compliance</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Owner / lawyer</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Holding shops' prepaid money</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Legal review of the shop prepaid wallet; at least a seller-terms clause.</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>NEW-033, NEW-034</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Owner / lawyer</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Agreement</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>GS1 India and brand permissions</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Agreement / written permission and a real sample file for each source; then go-ahead for large-scale ingestion.</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>PMD-002, PMD-006</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Cashfree live keys and Refunds API</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Set CASHFREE_APP_ID / CASHFREE_SECRET_KEY / CASHFREE_ENV=production and confirm the Refunds API is enabled - the Rs 1 bank-account check refunds every payment.</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>NEW-041</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Tile Board: build the four entries that have no feature behind them?</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Customer Favourites, App theme, Call rider (rider number is not shown to customers today); shop owner Theme. The board shows the nearest real page in their place.</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>NEW-046</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Translate the body of inner pages into Hindi / Marathi?</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Boards, header, menus, tabs and error screens are translated; forms, tables and policy pages are English. Thousands of strings; needs a native-speaker review.</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>GAP-015; NEW-047</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Decision / vendor</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Inventory &amp; Accounting: licensed GSP for GST returns</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Choose and contract a GSP (Masters India, ClearTax, IRIS, Tally GSP, Vayana) for live GSTR-2B/2A/1 pull; until then owners upload the file from gst.gov.in (works on production).</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>IA-022, IA-023</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Inventory &amp; Accounting: AI reading of supplier bills</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Allow bills to be read by Claude (ANTHROPIC_API_KEY + INVOICE_EXTRACTION_PROVIDER=claude): needed for photos, handwriting, Hindi and Marathi. Without it: e-invoice, Excel, PDF text and typing.</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>IA-034, IA-039</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Inventory &amp; Accounting: bill forwarding by email and S3 bucket</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Inbound mail provider (INBOUND_EMAIL_SECRET / _DOMAIN) for forwarding; S3-compatible bucket credentials (ACCOUNTS_S3_*) - bills stay in the database until then.</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>IA-032, IA-049</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G21"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -17522,26 +17838,26 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Go-live blocker</t>
+          <t>Owner inputs</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Email sending capacity</t>
+          <t>Inputs for PR #92 modules 2 and 3</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>The test site hit the mail host's hourly cap (451). Raise the limit or use a transactional email service before go-live; check SPF/DKIM for gokesari.com.</t>
+          <t>Modules 2 and 3 are on gokesari.com since #120 (module 2 on mock providers, module 3 switched off). Inputs P1-P6 are needed before using them for real.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>GAP-009, GS-055, NEW-039-042</t>
+          <t>NEW-037, NEW-038</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -17549,34 +17865,34 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Go-live blocker</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Rotate database passwords before go-live</t>
+          <t>Email sending capacity</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Urgent: the production Neon neondb_owner password was posted in a chat on 12 Oct - reset it now and update DATABASE_URL in hPanel (and the GitHub secrets). Rotate the other database passwords before go-live as planned.</t>
+          <t>The test site hit the mail host's hourly cap (451). Raise the limit or use a transactional email service before go-live; check SPF/DKIM for gokesari.com.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Go-live</t>
+          <t>GAP-009, GS-055, NEW-039-042</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -17592,26 +17908,26 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Owner inputs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Delete the downloaded copy-shops SQL files</t>
+          <t>referrals@gokesari.com and referral codes</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>copy-shops-1-PREVIEW.sql / copy-shops-2-APPLY.sql hold the 5 owners' contact details - delete every downloaded copy.</t>
+          <t>Create the mailbox and confirm mail arrives (not readable from the test run); decide who else gets requests (shopReferral.notifyEmails); create referral codes before switching shopReferral.required on.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>PLT-018</t>
+          <t>NEW-042</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -17619,34 +17935,34 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Release blocker</t>
+          <t>Accounts</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Bulk product upload: production checks signed in</t>
+          <t>App store publishing</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Live on gokesari.com since 15 Oct 15:58 UTC (#179). A signed-in import on production needs a designated test shop; the Production database workflow needs its repository variables set.</t>
+          <t>Expo account + EAS project id in mobile/app.config.ts; Google Play Console ($25) with the first .aab uploaded by hand; Apple Developer Program ($99/yr); store listings (privacy policy URL, Data safety form, screenshots). Then set MOBILE_* env vars for deep links. Update 14 Oct: the 'iPhone app' workflow (#153) is ready; it needs EXPO_TOKEN, ASC_API_KEY_P8, ASC_KEY_ID, ASC_ISSUER_ID, APPLE_TEAM_ID, the Expo project id and the App Store Connect app record. 18 Oct: store publishing ON HOLD by owner decision.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>BPU-16</t>
+          <t>NEW-043, NEW-044</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -17654,49 +17970,504 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>ON HOLD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Rotate database passwords before go-live</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Urgent: the production Neon neondb_owner password was posted in a chat on 12 Oct - reset it now and update DATABASE_URL in hPanel (and the GitHub secrets). Rotate the other database passwords before go-live as planned.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Go-live</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Delete the downloaded copy-shops SQL files</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>copy-shops-1-PREVIEW.sql / copy-shops-2-APPLY.sql hold the 5 owners' contact details - delete every downloaded copy.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>PLT-018</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Copied shops: sign-in, legal documents, two shops without location</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>The 5 copied owners sign in on gokesari.com and upload their legal documents; add map locations for the 2 original production shops (Asmy super market x2) so Nearby can list them.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>PLT-018, NEW-057, NEW-040</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Production order-lifecycle run (real payment)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>For QA-009: a production shop with delivery on and its owner's sign-in email; an approved rider (or permission to register one for approval); confirmation that the Cashfree live keys are set; the owner pays the small real top-up. No test data or sandbox keys on gokesari.com. Listed again in Owner inputs §14 (18 Oct).</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>QA-009</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Go-live blocker</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Bulk upload: mobile store builds</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>EAS / Expo account and Apple Developer account for the AAB and the iPhone build</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>BPU-10, BPU-11</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Owner action</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Accounting: INTEGRATION_ENCRYPTION_KEY value</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>The variable is set on test and production but is not base64 of 32 bytes (test reports encryption not configured; GST link answers 500). Set `openssl rand -base64 32` (a different value per site) in Hostinger and redeploy.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>IA-056, IA-020, IA-048, NEW-037</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Owner action</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Accounting: crons</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Schedule POST /api/cron/gst-reminders daily and /api/cron/bill-captures every 10 min (Bearer CRON_SECRET) on both sites.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>IA-027, IA-050</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Payment gateway live keys and webhook secrets</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT_GATEWAY + Cashfree (or Razorpay / PhonePe) live keys; payment and payout webhook secrets</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>GS-028, GS-073, SM-005, WF-001, NAV-003, NEW-007, GS-058</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Payout account and keys</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>RazorpayX / Cashfree payout account and keys for the 5-day shop payouts</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>GAP-005</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>GoKesari GSTIN, legal details and invoice prefix</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>For GoKesari fee invoices (F10.2.5)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>GAP-006</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Grievance Officer details</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Name, contact and address to publish on the grievance portal (consumer protection rules)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>SM-006</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Deep links: Android signing fingerprint and Apple Team ID</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>MOBILE_* values so gokesari.com links open the app</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>NEW-044</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Mobile push keys</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>EAS project + FCM / APNs keys for real push notifications (app 1.2.0)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>GS-074, NEW-043</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Owner inputs</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Batch cron jobs on both sites</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>payments-reconcile (5 min), auth-housekeeping, timeout-sweep, payouts and the other entries in crontab.txt</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>GS-028, GAP-004, GAP-005</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>